--- a/sheets/민요/검수/사철가 (채보2).xlsx
+++ b/sheets/민요/검수/사철가 (채보2).xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -627,13 +627,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -931,13 +931,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1080,13 +1080,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I16" s="2"/>
@@ -1225,13 +1225,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1375,13 +1375,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1450,13 +1450,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1601,13 +1601,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―</t>
+          <t xml:space="preserve">汰|–</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2135,13 +2135,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2292,13 +2292,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2441,13 +2441,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -2593,13 +2593,13 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2742,13 +2742,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3045,13 +3045,13 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I68" s="2"/>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I75" s="2"/>
@@ -3332,13 +3332,13 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I76" s="2"/>
@@ -3476,13 +3476,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I80" s="2"/>
@@ -3657,15 +3657,15 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -3683,7 +3683,7 @@
       <c r="H5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       <c r="J5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -3808,7 +3808,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -3844,7 +3844,7 @@
       <c r="D9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="H9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="2"/>
@@ -4013,14 +4013,14 @@
       <c r="B13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       <c r="F13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4053,7 +4053,7 @@
       <c r="J13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       <c r="H15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       <c r="B17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="C17" s="2"/>
@@ -4213,7 +4213,7 @@
       <c r="F17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       <c r="J17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="K17" s="2"/>

--- a/sheets/민요/검수/사철가 (채보2).xlsx
+++ b/sheets/민요/검수/사철가 (채보2).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3550,71 +3579,71 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">사철가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아기장</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">일년은</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3622,82 +3651,82 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="22"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="22"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="22"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="I4" s="22"/>
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="24"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="22"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나리</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="22"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -3705,41 +3734,41 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 潢</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -3747,50 +3776,50 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="22"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">열두</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3798,89 +3827,89 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 潢</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="22"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="22"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="22"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="22"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
+      <c r="K8" s="22"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">달래</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">또에</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -3888,88 +3917,88 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 仲</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="22"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="22"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="22"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="22"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사시절</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">종을</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -3977,86 +4006,86 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="K12" s="2"/>
+      <c r="K12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="22"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">들래</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">젓구가</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">종을씨</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4064,90 +4093,90 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="22"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="22"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="24"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="22"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
+      <c r="K14" s="22"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">봄바</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">분명쿠</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구우</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -4155,125 +4184,125 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="22"/>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="22"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="G16" s="22"/>
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="I16" s="3"/>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="I16" s="24"/>
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="K16" s="2"/>
+      <c r="K16" s="22"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="22"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">감에</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="K17" s="2"/>
+      <c r="K17" s="22"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="22"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="22"/>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="22"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="I18" s="22"/>
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K18" s="2"/>
+      <c r="K18" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/사철가 (채보2).xlsx
+++ b/sheets/민요/검수/사철가 (채보2).xlsx
@@ -3562,22 +3562,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="K4" s="24"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="K8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/사철가 (채보2).xlsx
+++ b/sheets/민요/검수/사철가 (채보2).xlsx
@@ -617,12 +617,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I3" s="3"/>
@@ -775,12 +775,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -925,12 +925,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I19" s="2"/>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I51" s="2"/>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -3659,7 +3659,7 @@
       <c r="C4" s="22"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E4" s="22"/>
@@ -3671,13 +3671,13 @@
       <c r="G4" s="22"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I4" s="22"/>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K4" s="24"/>
@@ -3851,13 +3851,13 @@
       <c r="G8" s="22"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K8" s="22"/>
@@ -4014,7 +4014,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -4032,7 +4032,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -4214,7 +4214,7 @@
       <c r="I16" s="24"/>
       <c r="J16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K16" s="22"/>

--- a/sheets/민요/검수/사철가 (채보2).xlsx
+++ b/sheets/민요/검수/사철가 (채보2).xlsx
@@ -2361,12 +2361,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -3541,12 +3541,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I81" s="2"/>
@@ -4273,7 +4273,7 @@
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C18" s="22"/>
@@ -4286,7 +4286,7 @@
       <c r="E18" s="22"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G18" s="22"/>

--- a/sheets/민요/검수/사철가 (채보2).xlsx
+++ b/sheets/민요/검수/사철가 (채보2).xlsx
@@ -3604,7 +3604,9 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아기장</t>
+          <t xml:space="preserve">아
+기
+장</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -3625,7 +3627,9 @@
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">일년은</t>
+          <t xml:space="preserve">일
+년
+은</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -3699,7 +3703,8 @@
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">나리</t>
+          <t xml:space="preserve">나
+리</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -3801,7 +3806,8 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">열두</t>
+          <t xml:space="preserve">열
+두</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -3878,7 +3884,8 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">달래</t>
+          <t xml:space="preserve">달
+래</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -3889,7 +3896,8 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">또에</t>
+          <t xml:space="preserve">또
+에</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -3979,7 +3987,9 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">사시절</t>
+          <t xml:space="preserve">사
+시
+절</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -3990,7 +4000,8 @@
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">종을</t>
+          <t xml:space="preserve">종
+을</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -4054,7 +4065,8 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">들래</t>
+          <t xml:space="preserve">들
+래</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -4065,7 +4077,9 @@
       </c>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">젓구가</t>
+          <t xml:space="preserve">젓
+구
+가</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -4076,7 +4090,9 @@
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">종을씨</t>
+          <t xml:space="preserve">종
+을
+씨</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -4146,7 +4162,8 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">봄바</t>
+          <t xml:space="preserve">봄
+바</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -4157,7 +4174,9 @@
       </c>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">분명쿠</t>
+          <t xml:space="preserve">분
+명
+쿠</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -4168,7 +4187,8 @@
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">구우</t>
+          <t xml:space="preserve">구
+우</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -4236,7 +4256,8 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">감에</t>
+          <t xml:space="preserve">감
+에</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">

--- a/sheets/민요/검수/사철가 (채보2).xlsx
+++ b/sheets/민요/검수/사철가 (채보2).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -224,6 +229,12 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3602,7 +3613,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 기
@@ -3614,7 +3625,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3625,7 +3636,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">일
 년
@@ -3637,7 +3648,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
@@ -3647,7 +3658,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3660,31 +3671,31 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="22"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E4" s="22"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G4" s="22"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" s="22"/>
+      <c r="I4" s="25"/>
       <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K4" s="24"/>
+      <c r="K4" s="26"/>
     </row>
     <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
@@ -3694,14 +3705,14 @@
 –</t>
         </is>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 리</t>
@@ -3713,14 +3724,14 @@
 仲</t>
         </is>
       </c>
-      <c r="G5" s="22"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -3731,7 +3742,7 @@
 –</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -3744,7 +3755,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
@@ -3752,28 +3763,28 @@
 潢</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="25"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -3787,13 +3798,13 @@
 無</t>
         </is>
       </c>
-      <c r="C7" s="22"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
@@ -3804,7 +3815,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">열
 두</t>
@@ -3815,7 +3826,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
@@ -3825,7 +3836,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3840,33 +3851,33 @@
 潢</t>
         </is>
       </c>
-      <c r="C8" s="22"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="E8" s="22"/>
+      <c r="E8" s="25"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G8" s="22"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" s="22"/>
+      <c r="I8" s="25"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K8" s="22"/>
+      <c r="K8" s="25"/>
     </row>
     <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
@@ -3875,14 +3886,14 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">달
 래</t>
@@ -3894,7 +3905,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">또
 에</t>
@@ -3906,7 +3917,7 @@
 –</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -3917,7 +3928,7 @@
 –</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -3932,33 +3943,33 @@
 仲</t>
         </is>
       </c>
-      <c r="C10" s="22"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="22"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="G10" s="22"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="22"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K10" s="22"/>
+      <c r="K10" s="25"/>
     </row>
     <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
@@ -3968,13 +3979,13 @@
 姑</t>
         </is>
       </c>
-      <c r="C11" s="22"/>
+      <c r="C11" s="25"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
@@ -3985,7 +3996,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사
 시
@@ -3998,7 +4009,7 @@
 –</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">종
 을</t>
@@ -4009,7 +4020,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -4022,31 +4033,31 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="25"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="25"/>
     </row>
     <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
@@ -4056,14 +4067,14 @@
 –</t>
         </is>
       </c>
-      <c r="C13" s="22"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">들
 래</t>
@@ -4075,7 +4086,7 @@
 –</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">젓
 구
@@ -4088,7 +4099,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">종
 을
@@ -4101,7 +4112,7 @@
 –</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4115,14 +4126,14 @@
 無</t>
         </is>
       </c>
-      <c r="C14" s="22"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="25"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
@@ -4130,20 +4141,20 @@
 潢</t>
         </is>
       </c>
-      <c r="G14" s="24"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I14" s="22"/>
+      <c r="I14" s="25"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K14" s="22"/>
+      <c r="K14" s="25"/>
     </row>
     <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
@@ -4153,14 +4164,14 @@
 無</t>
         </is>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="25"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">봄
 바</t>
@@ -4172,7 +4183,7 @@
 無</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">분
 명
@@ -4185,7 +4196,7 @@
 –</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구
 우</t>
@@ -4196,7 +4207,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -4210,34 +4221,34 @@
 仲</t>
         </is>
       </c>
-      <c r="C16" s="22"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E16" s="22"/>
+      <c r="E16" s="25"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G16" s="22"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="I16" s="24"/>
+      <c r="I16" s="26"/>
       <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K16" s="22"/>
+      <c r="K16" s="25"/>
     </row>
     <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
@@ -4247,14 +4258,14 @@
 –</t>
         </is>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">감
 에</t>
@@ -4266,7 +4277,7 @@
 –</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4277,7 +4288,7 @@
 南</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4288,7 +4299,7 @@
 –</t>
         </is>
       </c>
-      <c r="K17" s="22"/>
+      <c r="K17" s="25"/>
     </row>
     <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
@@ -4297,33 +4308,33 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="C18" s="22"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="E18" s="22"/>
+      <c r="E18" s="25"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G18" s="22"/>
+      <c r="G18" s="25"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="I18" s="22"/>
+      <c r="I18" s="25"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K18" s="22"/>
+      <c r="K18" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/사철가 (채보2).xlsx
+++ b/sheets/민요/검수/사철가 (채보2).xlsx
@@ -662,10 +662,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/사철가 (채보2).xlsx
+++ b/sheets/민요/검수/사철가 (채보2).xlsx
@@ -489,25 +489,9 @@
 에</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
+    <t xml:space="preserve">潢
+–
 –</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">사
@@ -515,24 +499,8 @@
 절</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">좋
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">은</t>
-    </r>
+    <t xml:space="preserve">좋
+은</t>
   </si>
   <si>
     <t xml:space="preserve">들
@@ -544,25 +512,9 @@
 가</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">좋
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">을
+    <t xml:space="preserve">좋
+을
 씨</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">봄
@@ -598,17 +550,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -735,7 +687,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -801,6 +753,58 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2501,276 +2505,276 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:K10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="18" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.48" customHeight="true">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+      <c r="B3" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+      <c r="B4" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="24"/>
+      <c r="H4" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="22" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+      <c r="B5" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="22"/>
+      <c r="D5" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+      <c r="B6" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="25"/>
+      <c r="D6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+      <c r="B7" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="10" t="s">
+      <c r="C7" s="21"/>
+      <c r="D7" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="26" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+      <c r="B8" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="24"/>
+      <c r="D8" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+      <c r="B9" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="22"/>
+      <c r="D9" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="22" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+      <c r="B10" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="25"/>
+      <c r="D10" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="12"/>
+      <c r="K10" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2778,7 +2782,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="92"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/사철가 (채보2).xlsx
+++ b/sheets/민요/검수/사철가 (채보2).xlsx
@@ -2511,20 +2511,20 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="18" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.48" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="40.82" customHeight="true">
       <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
@@ -2538,7 +2538,7 @@
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
       <c r="B3" s="20" t="s">
         <v>82</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
       <c r="B4" s="20" t="s">
         <v>124</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
       <c r="B5" s="20" t="s">
         <v>88</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
       <c r="B6" s="20" t="s">
         <v>91</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
       <c r="B7" s="20" t="s">
         <v>126</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
       <c r="B8" s="23" t="s">
         <v>97</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
       <c r="B9" s="20" t="s">
         <v>91</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
       <c r="B10" s="20" t="s">
         <v>102</v>
       </c>
@@ -2782,7 +2782,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="92"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="98"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
